--- a/app/reports/RGCO_research.xlsx
+++ b/app/reports/RGCO_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1526,10 +1526,10 @@
         <v>16.24</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>11.91</v>
+        <v>11.98</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="6">
@@ -1547,7 +1547,7 @@
         <v>373738496</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>15.942731</v>
+        <v>15.872807</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>10.686</v>
@@ -1670,10 +1670,10 @@
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>-164.771</v>
+        <v>-164.747</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>7.226</v>
+        <v>7.225</v>
       </c>
     </row>
     <row r="13">
@@ -1692,10 +1692,10 @@
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">
-        <v>-1.517</v>
+        <v>-1.537</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>0.599</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/RGCO_research.xlsx
+++ b/app/reports/RGCO_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-06 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-07 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
